--- a/samples/s17_带余额列_含红字.xlsx
+++ b/samples/s17_带余额列_含红字.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>邯郸市某某商贸有限公司  应收账款明细账</v>
+        <v>某市某某商贸有限公司  应收账款明细账</v>
       </c>
     </row>
     <row r="2">
